--- a/docs/Plano-de-Qualidade.xlsx
+++ b/docs/Plano-de-Qualidade.xlsx
@@ -2460,7 +2460,7 @@
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
-          <t>A confirmar pela equipe</t>
+          <t>Wagner Tiburcio</t>
         </is>
       </c>
     </row>

--- a/docs/Plano-de-Qualidade.xlsx
+++ b/docs/Plano-de-Qualidade.xlsx
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>Parcial em 26/10/2026: 100%. Testes de senha (hash bcrypt e ausência nas respostas) passando: test_driver_senha_hash.py e test_clientes*.py, CI verde.</t>
+          <t>Parcial em 27/10/2026: 100%. Testes de senha (hash bcrypt e ausência nas respostas) passando: test_driver_senha_hash.py e test_clientes*.py, CI verde.</t>
         </is>
       </c>
       <c r="J4" s="4" t="n"/>
@@ -808,7 +808,7 @@
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>Parcial em 26/10/2026: sem dados. Ainda não há rota protegida no main; login e sessão (GK-8) estão no PR #10.</t>
+          <t>Parcial em 27/10/2026: 100% da rota protegida que existe (GET /me, GK-8): teste de token ausente, inválido e expirado em test_autenticacao.py, CI verde. Perfil errado sem rota de administrador para testar ainda (Release 3).</t>
         </is>
       </c>
       <c r="J5" s="4" t="n"/>
@@ -918,7 +918,7 @@
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>Parcial em 26/10/2026: cadastro, catálogo e detalhe com exceções testadas (503 sem detalhes técnicos, jogo inexistente ou inativo, e-mail repetido). Falta a conferência do QA.</t>
+          <t>Parcial em 27/10/2026: cadastro, login, catálogo e detalhe com exceções testadas (503 sem detalhes técnicos, jogo inexistente ou inativo, e-mail repetido, segredo do token ausente). Falta a conferência do QA.</t>
         </is>
       </c>
       <c r="J7" s="4" t="n"/>
@@ -1028,7 +1028,7 @@
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>Parcial em 26/10/2026: cadastro devolve mensagem em português para e-mail repetido e senha curta. Falta o checklist do QA nas telas.</t>
+          <t>Parcial em 27/10/2026: cadastro e login devolvem mensagem em português (e-mail repetido, senha curta, e-mail ou senha incorretos). Falta o checklist do QA nas telas.</t>
         </is>
       </c>
       <c r="J9" s="4" t="n"/>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>Parcial em 26/10/2026: 0 bugs críticos ou altos abertos (nenhum bug registrado no Jira).</t>
+          <t>Parcial em 27/10/2026: 0 bugs críticos ou altos abertos (nenhum bug registrado no Jira).</t>
         </is>
       </c>
       <c r="J10" s="4" t="n"/>
@@ -1138,7 +1138,7 @@
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>Parcial em 26/10/2026: sem dados. Coluna Status do Plano de Teste ainda não preenchida.</t>
+          <t>Parcial em 27/10/2026: sem dados. Coluna Status do Plano de Teste ainda não preenchida.</t>
         </is>
       </c>
       <c r="J11" s="4" t="n"/>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>Parcial em 26/10/2026: 0 de 9 US adicionadas depois da Planning; ao menos 1 alterada (GK-57 ganhou o cenário 6 do DER em 21/10). Conferir no relatório da sprint.</t>
+          <t>Parcial em 27/10/2026: 0 de 9 US adicionadas depois da Planning; ao menos 1 alterada (GK-57 ganhou o cenário 6 do DER em 21/10). Conferir no relatório da sprint.</t>
         </is>
       </c>
       <c r="J13" s="4" t="n"/>
@@ -1299,7 +1299,7 @@
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>Parcial em 26/10/2026: 0% com revisão registrada no GitHub (0 de 9 PRs mesclados); 7 de 9 mesclados por outro integrante. Abaixo da meta.</t>
+          <t>Parcial em 27/10/2026: 0% com revisão registrada no GitHub (0 de 10 PRs mesclados); 8 de 10 mesclados por outro integrante. Abaixo da meta.</t>
         </is>
       </c>
       <c r="J14" s="4" t="n"/>
@@ -1354,7 +1354,7 @@
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>Parcial em 26/10/2026: 100% (23 de 23 execuções do CI verdes no main).</t>
+          <t>Parcial em 27/10/2026: 100% (29 de 29 execuções do CI verdes no main).</t>
         </is>
       </c>
       <c r="J15" s="4" t="n"/>
@@ -1405,7 +1405,7 @@
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>Parcial em 26/10/2026: 18 de 28 pontos concluídos (64%); a sprint termina em 29/10.</t>
+          <t>Parcial em 27/10/2026: 18 de 28 pontos concluídos (64%); GK-7 e GK-8 (8 pontos) em revisão com o código já no main. A sprint termina em 29/10.</t>
         </is>
       </c>
       <c r="J16" s="4" t="n"/>
@@ -1460,7 +1460,7 @@
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>Parcial em 26/10/2026: 0 erros (ruff check no main e no CI).</t>
+          <t>Parcial em 27/10/2026: 0 erros (ruff check no main e no CI).</t>
         </is>
       </c>
       <c r="J17" s="4" t="n"/>
@@ -1511,7 +1511,7 @@
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>Parcial em 26/10/2026: 100% (descrição, como executar e como testar no README).</t>
+          <t>Parcial em 27/10/2026: 100% (descrição, como executar e como testar no README).</t>
         </is>
       </c>
       <c r="J18" s="4" t="n"/>
@@ -1523,6 +1523,7 @@
         </is>
       </c>
     </row>
+    <row r="19"/>
     <row r="20">
       <c r="A20" s="8" t="inlineStr">
         <is>

--- a/docs/Plano-de-Qualidade.xlsx
+++ b/docs/Plano-de-Qualidade.xlsx
@@ -734,7 +734,7 @@
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>Parcial em 28/10/2026: 100% dos testes automatizados de senha aprovados (hash bcrypt e ausência nas respostas). Regressão local com 87/87 testes backend; CI da main 31/31 verde. Validação formal do QA pendente.</t>
+          <t>100% em 28/10/2026: testes de senha aprovados (hash bcrypt e ausência nas respostas); 87/87 backend e CI da main 32/32 verde. QA (Wagner) confirmou os testes, registro do SM na GK-80.</t>
         </is>
       </c>
       <c r="J4" s="4" t="n"/>
@@ -789,7 +789,7 @@
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>Parcial em 27/10/2026: 100% da rota protegida existente (GET /auth/me) coberta para token ausente, inválido e expirado. Perfil errado depende das rotas administrativas da Release 3. Validação formal do QA pendente.</t>
+          <t>100% da rota protegida existente (GET /auth/me) em 28/10/2026, coberta para token ausente, inválido e expirado (GK-71). Perfil errado depende das rotas administrativas da Release 3. QA confirmado, registro do SM na GK-83.</t>
         </is>
       </c>
       <c r="J5" s="4" t="n"/>
@@ -899,7 +899,7 @@
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>Parcial em 27/10/2026: cadastro, login, catálogo e detalhe com exceções automatizadas aprovadas; 87/87 backend, 27/27 E2E e 9/9 integrações. Falta a conferência formal do QA.</t>
+          <t>100% em 28/10/2026: cadastro, login, catálogo e detalhe com exceções tratadas; 87/87 backend, 27/27 E2E e 9/9 integrações. QA confirmado, registro do SM nas GK-80 e GK-83.</t>
         </is>
       </c>
       <c r="J7" s="4" t="n"/>
@@ -1009,7 +1009,7 @@
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>Parcial em 27/10/2026: cadastro e login mostram mensagens em português para duplicidade, senha curta e credenciais incorretas. Testes automatizados aprovados; falta o checklist do QA nas telas.</t>
+          <t>100% em 28/10/2026 nos testes automatizados: cadastro e login com mensagens em português para duplicidade, senha curta e credenciais incorretas (GK-76). QA confirmado pelo SM; checklist individual do QA não anexado.</t>
         </is>
       </c>
       <c r="J9" s="4" t="n"/>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>Parcial em 28/10/2026: 0 bugs críticos ou altos sem correção. GK-106 (Alta) foi corrigido na main pelo PR #13, mesclado em 28/10/2026 com CI verde; no Jira segue Em revisão até a validação do QA.</t>
+          <t>0 em 28/10/2026. GK-106 (Alta) corrigido na main pelo PR #13 e Concluído no Jira.</t>
         </is>
       </c>
       <c r="J10" s="4" t="n"/>
@@ -1119,7 +1119,7 @@
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>Parcial em 27/10/2026: regressão automatizada executada com 87/87 testes backend, 27/27 cenários E2E e 9/9 integrações. A coluna Status do Plano de Teste e a execução formal pelo QA permanecem pendentes.</t>
+          <t>Parcial em 28/10/2026: regressão automatizada com 87/87 backend, 27/27 E2E e 9/9 integrações; QA confirmado pelo SM. A coluna Status do Plano de Teste e os registros por caso do QA seguem pendentes.</t>
         </is>
       </c>
       <c r="J11" s="4" t="n"/>
@@ -1280,7 +1280,7 @@
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>Parcial em 28/10/2026: 0% com revisão registrada no GitHub (0 de 12 PRs mesclados); 9 de 12 mesclados por outro integrante. Abaixo da meta.</t>
+          <t>0% em 28/10/2026: 0 de 13 PRs mesclados com revisão registrada no GitHub; 10 de 13 mesclados por outro integrante. Abaixo da meta.</t>
         </is>
       </c>
       <c r="J14" s="4" t="n"/>
@@ -1335,7 +1335,7 @@
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>Parcial em 28/10/2026: 100% (31 de 31 execuções do CI verdes na main, incluindo os merges dos PRs #12 e #13).</t>
+          <t>100% em 28/10/2026 (32 de 32 execuções do CI verdes na main).</t>
         </is>
       </c>
       <c r="J15" s="4" t="n"/>
@@ -1386,7 +1386,7 @@
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>Parcial em 27/10/2026: 18 de 28 pontos concluídos no Jira (64%); GK-7 e GK-8 somam 8 pontos em revisão, com código integrado à main. Implementação técnica: 26 de 28 pontos; GK-60 e GK-61 seguem em andamento.</t>
+          <t>Em 28/10/2026, antes da Review: 27 de 28 pontos concluídos (96%), diferença de 4%, dentro da meta. GK-61 (1 ponto) Em revisão; valor final no fechamento da sprint.</t>
         </is>
       </c>
       <c r="J16" s="4" t="n"/>
@@ -1441,7 +1441,7 @@
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>Parcial em 27/10/2026: 0 erros no ruff local e no CI; regressão backend 87/87 aprovada.</t>
+          <t>0 erros em 28/10/2026 no ruff do CI da main (32/32 execuções verdes).</t>
         </is>
       </c>
       <c r="J17" s="4" t="n"/>

--- a/docs/Plano-de-Qualidade.xlsx
+++ b/docs/Plano-de-Qualidade.xlsx
@@ -1119,7 +1119,7 @@
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>Parcial em 28/10/2026: regressão automatizada com 87/87 backend, 27/27 E2E e 9/9 integrações; QA confirmado pelo SM. A coluna Status do Plano de Teste e os registros por caso do QA seguem pendentes.</t>
+          <t>100% em 28/10/2026: 30 de 30 casos do Plano de Teste executados e aprovados no CI da main (pytest 87/87, Cypress 27/27, integração 9/9); Status registrado no Plano de Teste v1.1.</t>
         </is>
       </c>
       <c r="J11" s="4" t="n"/>
@@ -1229,7 +1229,7 @@
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>Parcial em 27/10/2026: 0 de 9 US adicionadas depois da Planning; ao menos 1 alterada (GK-57 ganhou o cenário 6 do DER em 21/10). Conferir no relatório da sprint.</t>
+          <t>11% em 28/10/2026: 0 de 9 US adicionadas e 1 alterada (GK-57 ganhou o cenário 6 do DER em 21/10), dentro da meta.</t>
         </is>
       </c>
       <c r="J13" s="4" t="n"/>

--- a/docs/Plano-de-Qualidade.xlsx
+++ b/docs/Plano-de-Qualidade.xlsx
@@ -1,14 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Orientações" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Plano de qualidade" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Catálogo de métricas" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Revisões" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Orientações" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Plano de qualidade" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Catálogo de métricas" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Revisões" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -729,7 +730,7 @@
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>QA - Wagner</t>
+          <t>QA - Rodrigo</t>
         </is>
       </c>
       <c r="I4" s="4" t="inlineStr">
@@ -784,7 +785,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>QA - Wagner</t>
+          <t>QA - Rodrigo</t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
@@ -839,7 +840,7 @@
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>QA - Wagner</t>
+          <t>QA - Rodrigo</t>
         </is>
       </c>
       <c r="I6" s="4" t="inlineStr">
@@ -894,7 +895,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>QA - Wagner</t>
+          <t>QA - Rodrigo</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
@@ -949,7 +950,7 @@
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>QA - Wagner e PO - Pedro</t>
+          <t>QA - Rodrigo e PO - Wagner</t>
         </is>
       </c>
       <c r="I8" s="4" t="inlineStr">
@@ -1004,7 +1005,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>QA - Wagner</t>
+          <t>QA - Rodrigo</t>
         </is>
       </c>
       <c r="I9" s="4" t="inlineStr">
@@ -1059,7 +1060,7 @@
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>QA - Wagner</t>
+          <t>QA - Rodrigo</t>
         </is>
       </c>
       <c r="I10" s="4" t="inlineStr">
@@ -1114,7 +1115,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>QA - Wagner</t>
+          <t>QA - Rodrigo</t>
         </is>
       </c>
       <c r="I11" s="4" t="inlineStr">
@@ -1169,7 +1170,7 @@
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>PO - Pedro</t>
+          <t>PO - Wagner</t>
         </is>
       </c>
       <c r="I12" s="4" t="inlineStr">
@@ -1224,7 +1225,7 @@
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>PO - Pedro</t>
+          <t>PO - Wagner</t>
         </is>
       </c>
       <c r="I13" s="4" t="inlineStr">
@@ -1275,7 +1276,7 @@
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>SM - Rodrigo</t>
+          <t>SM - Pedro</t>
         </is>
       </c>
       <c r="I14" s="4" t="inlineStr">
@@ -1330,7 +1331,7 @@
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>DevOps - Pedro</t>
+          <t>DevOps - Wagner</t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
@@ -1381,7 +1382,7 @@
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>SM - Rodrigo</t>
+          <t>SM - Pedro</t>
         </is>
       </c>
       <c r="I16" s="4" t="inlineStr">
@@ -1436,7 +1437,7 @@
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>DevOps - Pedro</t>
+          <t>DevOps - Wagner</t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
@@ -1487,7 +1488,7 @@
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>DevOps - Pedro</t>
+          <t>DevOps - Wagner</t>
         </is>
       </c>
       <c r="I18" s="4" t="inlineStr">
@@ -2443,13 +2444,37 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="7" t="n"/>
-      <c r="B5" s="7" t="n"/>
-      <c r="C5" s="7" t="n"/>
-      <c r="D5" s="7" t="n"/>
-      <c r="E5" s="7" t="n"/>
-      <c r="F5" s="7" t="n"/>
+    <row r="5" ht="45" customHeight="1" s="10">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>29/10/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>Coluna Responsável (Q-01 a Q-15)</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>Responsáveis trocados para os papéis da Release 2: QA Rodrigo, PO e DevOps Wagner, SM Pedro. Metas, métricas e formas de medição sem mudança.</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>Rodízio de papéis no fim da Release 1 (README). Os resultados R1 seguem com os responsáveis da Release 1.</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>A aprovar na Planning da Sprint 2 (03/11/2026)</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n"/>
